--- a/experiments_logs/HAR_experiments/test1/train_linear_1p_seed_0/test1_train_linear_1p_seed_0_classification_report.xlsx
+++ b/experiments_logs/HAR_experiments/test1/train_linear_1p_seed_0/test1_train_linear_1p_seed_0_classification_report.xlsx
@@ -487,34 +487,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69.42148760330579</v>
+        <v>58.11320754716981</v>
       </c>
       <c r="C2" t="n">
-        <v>89.47368421052632</v>
+        <v>88.53503184713377</v>
       </c>
       <c r="D2" t="n">
-        <v>29.03225806451613</v>
+        <v>73.20954907161804</v>
       </c>
       <c r="E2" t="n">
-        <v>97.46835443037975</v>
+        <v>76.5</v>
       </c>
       <c r="F2" t="n">
-        <v>69.61770623742454</v>
+        <v>63.46433770014556</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>97.92843691148776</v>
       </c>
       <c r="H2" t="n">
-        <v>57.61791652527995</v>
+        <v>72.58228707159824</v>
       </c>
       <c r="I2" t="n">
-        <v>75.83558175769208</v>
+        <v>76.29176051292582</v>
       </c>
       <c r="J2" t="n">
-        <v>77.1504218680423</v>
+        <v>76.41135386203671</v>
       </c>
       <c r="K2" t="n">
-        <v>49.47732795567271</v>
+        <v>66.97934357679216</v>
       </c>
     </row>
     <row r="3">
@@ -524,34 +524,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67.74193548387096</v>
+        <v>93.14516129032258</v>
       </c>
       <c r="C3" t="n">
-        <v>3.609341825902336</v>
+        <v>29.51167728237792</v>
       </c>
       <c r="D3" t="n">
-        <v>92.14285714285714</v>
+        <v>65.71428571428571</v>
       </c>
       <c r="E3" t="n">
-        <v>15.68228105906314</v>
+        <v>62.32179226069247</v>
       </c>
       <c r="F3" t="n">
-        <v>65.0375939849624</v>
+        <v>81.95488721804512</v>
       </c>
       <c r="G3" t="n">
-        <v>99.62756052141528</v>
+        <v>96.8342644320298</v>
       </c>
       <c r="H3" t="n">
-        <v>57.61791652527995</v>
+        <v>72.58228707159824</v>
       </c>
       <c r="I3" t="n">
-        <v>57.30692833634521</v>
+        <v>71.58034469962558</v>
       </c>
       <c r="J3" t="n">
-        <v>57.61791652527995</v>
+        <v>72.58228707159824</v>
       </c>
       <c r="K3" t="n">
-        <v>49.47732795567271</v>
+        <v>66.97934357679216</v>
       </c>
     </row>
     <row r="4">
@@ -561,34 +561,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68.57142857142856</v>
+        <v>71.57242447714948</v>
       </c>
       <c r="C4" t="n">
-        <v>6.938775510204081</v>
+        <v>44.26751592356688</v>
       </c>
       <c r="D4" t="n">
-        <v>44.15288077581289</v>
+        <v>69.25972396486826</v>
       </c>
       <c r="E4" t="n">
-        <v>27.01754385964912</v>
+        <v>68.68686868686868</v>
       </c>
       <c r="F4" t="n">
-        <v>67.24975704567541</v>
+        <v>71.53404429860542</v>
       </c>
       <c r="G4" t="n">
-        <v>99.81343283582089</v>
+        <v>97.37827715355806</v>
       </c>
       <c r="H4" t="n">
-        <v>57.61791652527995</v>
+        <v>72.58228707159824</v>
       </c>
       <c r="I4" t="n">
-        <v>52.29063643309849</v>
+        <v>70.4498090841028</v>
       </c>
       <c r="J4" t="n">
-        <v>53.77200542205598</v>
+        <v>71.09348677620704</v>
       </c>
       <c r="K4" t="n">
-        <v>49.47732795567271</v>
+        <v>66.97934357679216</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         <v>53700</v>
       </c>
       <c r="H5" t="n">
-        <v>57.61791652527995</v>
+        <v>72.58228707159824</v>
       </c>
       <c r="I5" t="n">
         <v>294700</v>
@@ -625,7 +625,7 @@
         <v>294700</v>
       </c>
       <c r="K5" t="n">
-        <v>49.47732795567271</v>
+        <v>66.97934357679216</v>
       </c>
     </row>
   </sheetData>
